--- a/output/pdf_financials_xlsx/RBY.xlsx
+++ b/output/pdf_financials_xlsx/RBY.xlsx
@@ -3195,13 +3195,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-1.547</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-26.581</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-21.028</v>
       </c>
       <c r="E118" s="1" t="inlineStr">
         <is>
@@ -7910,7 +7910,11 @@
           <t>Exploration and evaluation expense (note 6)</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -8273,7 +8277,11 @@
           <t>Exploration and evaluation expenditures (note 6)</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E116" s="5" t="n">
         <v>-1.547</v>
       </c>

--- a/output/pdf_financials_xlsx/RBY.xlsx
+++ b/output/pdf_financials_xlsx/RBY.xlsx
@@ -1275,7 +1275,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.002555</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.002555</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0</v>
@@ -1583,7 +1583,7 @@
         <v>10.231</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.018365</v>
+        <v>0.01581</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.012688</v>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">

--- a/output/pdf_financials_xlsx/RBY.xlsx
+++ b/output/pdf_financials_xlsx/RBY.xlsx
@@ -501,15 +501,11 @@
       <c r="D4" s="3" t="n">
         <v>80.455</v>
       </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E4" s="3" t="n">
+        <v>0.148112</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0.209246</v>
       </c>
     </row>
     <row r="5">
@@ -527,15 +523,11 @@
       <c r="D5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -553,15 +545,11 @@
       <c r="D6" s="3" t="n">
         <v>80.455</v>
       </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E6" s="3" t="n">
+        <v>0.148112</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0.209246</v>
       </c>
     </row>
     <row r="7">
@@ -579,15 +567,11 @@
       <c r="D7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -605,15 +589,11 @@
       <c r="D8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -631,15 +611,11 @@
       <c r="D9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -657,15 +633,11 @@
       <c r="D10" s="3" t="n">
         <v>28.654</v>
       </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E10" s="3" t="n">
+        <v>0.066409</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0.052784</v>
       </c>
     </row>
     <row r="11">
@@ -683,15 +655,11 @@
       <c r="D11" s="3" t="n">
         <v>51.801</v>
       </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E11" s="3" t="n">
+        <v>0.081703</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0.156462</v>
       </c>
     </row>
     <row r="12">
@@ -709,15 +677,11 @@
       <c r="D12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -735,15 +699,11 @@
       <c r="D13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -761,15 +721,11 @@
       <c r="D14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -787,15 +743,11 @@
       <c r="D15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E15" s="3" t="n">
+        <v>0.000178</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0.000827</v>
       </c>
     </row>
     <row r="16">
@@ -813,15 +765,11 @@
       <c r="D16" s="3" t="n">
         <v>26.603</v>
       </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E16" s="3" t="n">
+        <v>0.059033</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>0.041441</v>
       </c>
     </row>
     <row r="17">
@@ -839,15 +787,11 @@
       <c r="D17" s="3" t="n">
         <v>-8.042</v>
       </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E17" s="3" t="n">
+        <v>-0.00906</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-0.008884</v>
       </c>
     </row>
     <row r="18">
@@ -929,15 +873,11 @@
       <c r="D20" s="3" t="n">
         <v>18.561</v>
       </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E20" s="3" t="n">
+        <v>0.049973</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>0.032557</v>
       </c>
     </row>
     <row r="21">
@@ -955,15 +895,11 @@
       <c r="D21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -981,15 +917,11 @@
       <c r="D22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1007,15 +939,11 @@
       <c r="D23" s="3" t="n">
         <v>18.561</v>
       </c>
-      <c r="E23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E23" s="3" t="n">
+        <v>0.049973</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>0.032557</v>
       </c>
     </row>
     <row r="24">
@@ -1033,15 +961,11 @@
       <c r="D24" s="3" t="n">
         <v>0.31</v>
       </c>
-      <c r="E24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E24" s="3" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="25">
@@ -1059,15 +983,11 @@
       <c r="D25" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="E25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E25" s="3" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>0.34</v>
       </c>
     </row>
     <row r="26">
@@ -1085,15 +1005,11 @@
       <c r="D26" s="3" t="n">
         <v>61.87</v>
       </c>
-      <c r="E26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E26" s="3" t="n">
+        <v>0.069407</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>0.09575599999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1111,15 +1027,11 @@
       <c r="D27" s="3" t="n">
         <v>26.603</v>
       </c>
-      <c r="E27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E27" s="3" t="n">
+        <v>0.059033</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>0.041441</v>
       </c>
     </row>
     <row r="28">
@@ -1137,15 +1049,11 @@
       <c r="D28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E28" s="3" t="n">
+        <v>0.049847</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>0.09424299999999999</v>
       </c>
     </row>
     <row r="29">
@@ -1163,15 +1071,11 @@
       <c r="D29" s="3" t="n">
         <v>26.603</v>
       </c>
-      <c r="E29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E29" s="3" t="n">
+        <v>0.10888</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>0.135684</v>
       </c>
     </row>
     <row r="30">
@@ -1189,15 +1093,11 @@
       <c r="D30" s="3" t="n">
         <v>33.06568889441303</v>
       </c>
-      <c r="E30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E30" s="3" t="n">
+        <v>73.51193691260669</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>64.84425030824961</v>
       </c>
     </row>
     <row r="31">
@@ -1215,15 +1115,11 @@
       <c r="D31" s="3" t="n">
         <v>30.22967334511145</v>
       </c>
-      <c r="E31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E31" s="3" t="n">
+        <v>15.34734809343926</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>21.43770661904877</v>
       </c>
     </row>
     <row r="32">
@@ -1241,15 +1137,11 @@
       <c r="D32" s="3" t="n">
         <v>23.07003915232117</v>
       </c>
-      <c r="E32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E32" s="3" t="n">
+        <v>33.74000756184509</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>15.559198264244</v>
       </c>
     </row>
     <row r="33">
@@ -2077,10 +1969,10 @@
         <v>0</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>0.000357</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>0.000389</v>
       </c>
     </row>
     <row r="71">
@@ -2099,10 +1991,10 @@
         <v>0</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0</v>
+        <v>0.000357</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0</v>
+        <v>0.000389</v>
       </c>
     </row>
     <row r="72">
@@ -2187,10 +2079,10 @@
         <v>0.077</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.014229</v>
+        <v>0.013872</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.0105</v>
+        <v>0.010111</v>
       </c>
     </row>
     <row r="76">
@@ -2302,15 +2194,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E80" s="3" t="n">
+        <v>0.001151549753723183</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>0.001131030953613193</v>
       </c>
     </row>
     <row r="81">
@@ -2709,15 +2597,11 @@
       <c r="D99" s="3" t="n">
         <v>18.561</v>
       </c>
-      <c r="E99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E99" s="3" t="n">
+        <v>0.049973</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>0.032557</v>
       </c>
     </row>
     <row r="100">
@@ -2735,15 +2619,11 @@
       <c r="D100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2761,15 +2641,11 @@
       <c r="D101" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -2787,15 +2663,11 @@
       <c r="D102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2813,15 +2685,11 @@
       <c r="D103" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -2839,15 +2707,11 @@
       <c r="D104" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -2865,15 +2729,11 @@
       <c r="D105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2891,15 +2751,11 @@
       <c r="D106" s="3" t="n">
         <v>1.237</v>
       </c>
-      <c r="E106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E106" s="3" t="n">
+        <v>0.003093</v>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>-0.004562</v>
       </c>
     </row>
     <row r="107">
@@ -2917,15 +2773,11 @@
       <c r="D107" s="3" t="n">
         <v>3.041</v>
       </c>
-      <c r="E107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E107" s="3" t="n">
+        <v>0.002939</v>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>0.002166</v>
       </c>
     </row>
     <row r="108">
@@ -2943,15 +2795,11 @@
       <c r="D108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2969,15 +2817,11 @@
       <c r="D109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2995,15 +2839,11 @@
       <c r="D110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -3021,15 +2861,11 @@
       <c r="D111" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -3047,15 +2883,11 @@
       <c r="D112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -3073,15 +2905,11 @@
       <c r="D113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -3099,15 +2927,11 @@
       <c r="D114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -3125,15 +2949,11 @@
       <c r="D115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -3151,15 +2971,11 @@
       <c r="D116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -3177,15 +2993,11 @@
       <c r="D117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -3203,15 +3015,11 @@
       <c r="D118" s="3" t="n">
         <v>-21.028</v>
       </c>
-      <c r="E118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E118" s="3" t="n">
+        <v>-0.015129</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>-0.007373</v>
       </c>
     </row>
     <row r="119">
@@ -3229,15 +3037,11 @@
       <c r="D119" s="3" t="n">
         <v>-94.354</v>
       </c>
-      <c r="E119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E119" s="3" t="n">
+        <v>-0.17303</v>
+      </c>
+      <c r="F119" s="3" t="n">
+        <v>-0.115058</v>
       </c>
     </row>
     <row r="120">
@@ -3255,15 +3059,11 @@
       <c r="D120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -3281,15 +3081,11 @@
       <c r="D121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -3307,15 +3103,11 @@
       <c r="D122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -3333,15 +3125,11 @@
       <c r="D123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -3359,15 +3147,11 @@
       <c r="D124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -3385,15 +3169,11 @@
       <c r="D125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -3411,15 +3191,11 @@
       <c r="D126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -3469,15 +3245,11 @@
       <c r="D128" s="3" t="n">
         <v>-0.254</v>
       </c>
-      <c r="E128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -3495,15 +3267,11 @@
       <c r="D129" s="3" t="n">
         <v>37.013</v>
       </c>
-      <c r="E129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E129" s="3" t="n">
+        <v>0.07979700000000001</v>
+      </c>
+      <c r="F129" s="3" t="n">
+        <v>-0.016293</v>
       </c>
     </row>
     <row r="130">
@@ -3521,15 +3289,11 @@
       <c r="D130" s="3" t="n">
         <v>1.95</v>
       </c>
-      <c r="E130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E130" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" s="3" t="n">
+        <v>0.002555</v>
       </c>
     </row>
     <row r="131">
@@ -3547,15 +3311,11 @@
       <c r="D131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -3573,15 +3333,11 @@
       <c r="D132" s="3" t="n">
         <v>-1.95</v>
       </c>
-      <c r="E132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E132" s="3" t="n">
+        <v>0.002555</v>
+      </c>
+      <c r="F132" s="3" t="n">
+        <v>-0.002555</v>
       </c>
     </row>
     <row r="133">
@@ -3599,15 +3355,11 @@
       <c r="D133" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E133" s="3" t="n">
+        <v>0.002555</v>
+      </c>
+      <c r="F133" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -3625,15 +3377,11 @@
       <c r="D134" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -3651,15 +3399,11 @@
       <c r="D135" s="3" t="n">
         <v>55.391</v>
       </c>
-      <c r="E135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E135" s="3" t="n">
+        <v>0.095788</v>
+      </c>
+      <c r="F135" s="3" t="n">
+        <v>0.128796</v>
       </c>
     </row>
   </sheetData>
@@ -3673,7 +3417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I184"/>
+  <dimension ref="A1:I223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4303,7 +4047,11 @@
           <t>Lease liabilities (note 7)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -7584,35 +7332,33 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>RUBELLITE ENERGY INC.</t>
+          <t>Cash flows from operating activities</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Years Ended December 31, 2023 December</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net income $</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="n">
+        <v>7.702</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>2.022</v>
+        <v>24.605</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>18.561</v>
+      </c>
+      <c r="H99" s="5" t="n">
+        <v>0.049973</v>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>0.032557</v>
       </c>
     </row>
     <row r="100">
@@ -7623,37 +7369,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Cash flows from operating activities</t>
+          <t>Adjustments to add (deduct)</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Net income $</t>
+          <t>Depletion and depreciation (note 4, 6)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E100" s="5" t="n">
-        <v>7.702</v>
-      </c>
-      <c r="F100" s="5" t="n">
-        <v>24.605</v>
-      </c>
-      <c r="G100" s="5" t="n">
-        <v>18.561</v>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="n">
+        <v>0.049847</v>
+      </c>
+      <c r="I100" s="5" t="n">
+        <v>0.09424299999999999</v>
       </c>
     </row>
     <row r="101">
@@ -7664,37 +7412,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Adjustments to add (deduct) non-cash items</t>
+          <t>Adjustments to add (deduct)</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Depletion (note 5)</t>
+          <t>Share based payments (note 10)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Depletion</t>
-        </is>
-      </c>
-      <c r="E101" s="5" t="n">
-        <v>1.389</v>
-      </c>
-      <c r="F101" s="5" t="n">
-        <v>13.462</v>
-      </c>
-      <c r="G101" s="5" t="n">
-        <v>27.485</v>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="n">
+        <v>0.003571</v>
+      </c>
+      <c r="I101" s="5" t="n">
+        <v>0.005368</v>
       </c>
     </row>
     <row r="102">
@@ -7705,37 +7455,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Adjustments to add (deduct) non-cash items</t>
+          <t>Adjustments to add (deduct)</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Share-based payments (note 9)</t>
+          <t>Deferred tax expense (note 14)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E102" s="5" t="n">
-        <v>0.307</v>
-      </c>
-      <c r="F102" s="5" t="n">
-        <v>1.724</v>
-      </c>
-      <c r="G102" s="5" t="n">
-        <v>3.041</v>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H102" s="5" t="n">
+        <v>0.00906</v>
+      </c>
+      <c r="I102" s="5" t="n">
+        <v>0.008884</v>
       </c>
     </row>
     <row r="103">
@@ -7746,12 +7498,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Adjustments to add (deduct) non-cash items</t>
+          <t>Adjustments to add (deduct)</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Deferred tax expense (recovery) (note 12)</t>
+          <t>Unrealized loss on risk management contracts (note 17)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -7760,21 +7512,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F103" s="5" t="n">
-        <v>-14.797</v>
-      </c>
-      <c r="G103" s="5" t="n">
-        <v>8.042</v>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="n">
+        <v>0.012252</v>
+      </c>
+      <c r="I103" s="5" t="n">
+        <v>0.001721</v>
       </c>
     </row>
     <row r="104">
@@ -7785,12 +7537,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Adjustments to add (deduct) non-cash items</t>
+          <t>Adjustments to add (deduct)</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Unrealized gain on risk management contracts (note 15)</t>
+          <t>Non-cash finance expense (note 15)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -7799,21 +7551,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F104" s="5" t="n">
-        <v>-2.025</v>
-      </c>
-      <c r="G104" s="5" t="n">
-        <v>-8.651999999999999</v>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>0.000472</v>
+      </c>
+      <c r="I104" s="5" t="n">
+        <v>0.001754</v>
       </c>
     </row>
     <row r="105">
@@ -7824,33 +7576,35 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Adjustments to add (deduct) non-cash items</t>
+          <t>Adjustments to add (deduct)</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Finance - accretion on decommissioning obligations (note 7)</t>
+          <t>Gain on dispositions (note 4c)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
-      <c r="E105" s="5" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="F105" s="5" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="G105" s="5" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="n">
+        <v>-0.031617</v>
+      </c>
+      <c r="I105" s="5" t="n">
+        <v>-0.007791</v>
       </c>
     </row>
     <row r="106">
@@ -7861,12 +7615,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Adjustments to add (deduct) non-cash items</t>
+          <t>Adjustments to add (deduct)</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Gain on dispositions (note 4b)</t>
+          <t>Non-cash exploration and evaluation expense (note 5)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -7880,18 +7634,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G106" s="5" t="n">
-        <v>-1.29</v>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H106" s="5" t="n">
+        <v>0.00022</v>
+      </c>
+      <c r="I106" s="5" t="n">
+        <v>0.005425</v>
       </c>
     </row>
     <row r="107">
@@ -7902,17 +7654,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Adjustments to add (deduct) non-cash items</t>
+          <t>Adjustments to add (deduct)</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expense (note 6)</t>
+          <t>Payment for share based compensation (note 10)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NetOtherInvestingChanges</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -7925,18 +7677,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G107" s="5" t="n">
-        <v>6.842</v>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="n">
+        <v>-0.000632</v>
+      </c>
+      <c r="I107" s="5" t="n">
+        <v>-0.003202</v>
       </c>
     </row>
     <row r="108">
@@ -7947,12 +7697,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Adjustments to add (deduct) non-cash items</t>
+          <t>Adjustments to add (deduct)</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Decommissioning obligations settled (note 7)</t>
+          <t>Payment for other provision (note 8b)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -7966,18 +7716,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G108" s="5" t="n">
-        <v>-0.003</v>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I108" s="5" t="n">
+        <v>-0.00375</v>
       </c>
     </row>
     <row r="109">
@@ -7988,37 +7738,35 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Adjustments to add (deduct) non-cash items</t>
+          <t>Adjustments to add (deduct)</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital (note 14)</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>ChangeInWorkingCapital</t>
-        </is>
-      </c>
-      <c r="E109" s="5" t="n">
-        <v>-0.48</v>
-      </c>
-      <c r="F109" s="5" t="n">
-        <v>0.834</v>
-      </c>
-      <c r="G109" s="5" t="n">
-        <v>1.237</v>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Decommissioning obligations settled (note 8a)</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="n">
+        <v>-0.000451</v>
+      </c>
+      <c r="I109" s="5" t="n">
+        <v>-0.001851</v>
       </c>
     </row>
     <row r="110">
@@ -8029,37 +7777,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Adjustments to add (deduct) non-cash items</t>
+          <t>Adjustments to add (deduct)</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Net cash flows from operating activities</t>
+          <t>Change in non-cash working capital (note 16)</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E110" s="5" t="n">
-        <v>1.115</v>
-      </c>
-      <c r="F110" s="5" t="n">
-        <v>23.87</v>
-      </c>
-      <c r="G110" s="5" t="n">
-        <v>55.391</v>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H110" s="5" t="n">
+        <v>0.003093</v>
+      </c>
+      <c r="I110" s="5" t="n">
+        <v>-0.004562</v>
       </c>
     </row>
     <row r="111">
@@ -8070,35 +7820,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>Adjustments to add (deduct)</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Common shares issued (note 8)</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
+          <t>Net cash flows from operating activities</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F111" s="5" t="n">
-        <v>38.744</v>
-      </c>
-      <c r="G111" s="5" t="n">
-        <v>19.95</v>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H111" s="5" t="n">
+        <v>0.095788</v>
+      </c>
+      <c r="I111" s="5" t="n">
+        <v>0.128796</v>
       </c>
     </row>
     <row r="112">
@@ -8109,34 +7863,32 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>Cash flows from (used in) financing activities</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Share issue costs (note 8)</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
+          <t>Common shares issues, net of fees</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F112" s="5" t="n">
-        <v>-1.685</v>
-      </c>
-      <c r="G112" s="5" t="n">
-        <v>-0.254</v>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H112" s="5" t="n">
+        <v>-0.000624</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -8152,12 +7904,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>Cash flows from (used in) financing activities</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Change in revolving bank debt (note 11)</t>
+          <t>Term loan, net of issue costs (note 13)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -8166,16 +7918,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F113" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="G113" s="5" t="n">
-        <v>17.317</v>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="n">
+        <v>0.018964</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -8191,37 +7945,35 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>Cash flows from (used in) financing activities</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Net cash flows from financing activities</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
-      <c r="E114" s="5" t="n">
-        <v>81.333</v>
-      </c>
-      <c r="F114" s="5" t="n">
-        <v>49.059</v>
-      </c>
-      <c r="G114" s="5" t="n">
-        <v>37.013</v>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Payment lease liabilities (note 7)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H114" s="5" t="n">
+        <v>-7.1e-05</v>
+      </c>
+      <c r="I114" s="5" t="n">
+        <v>-0.000376</v>
       </c>
     </row>
     <row r="115">
@@ -8232,28 +7984,32 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Cash flows used in investing activities</t>
+          <t>Cash flows from (used in) financing activities</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Property, plant and equipment expenditures (note 5)</t>
+          <t>Repayment of acquired bank debt (note 4c)</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
-      <c r="E115" s="5" t="n">
-        <v>-15.811</v>
-      </c>
-      <c r="F115" s="5" t="n">
-        <v>-67.626</v>
-      </c>
-      <c r="G115" s="5" t="n">
-        <v>-43.66</v>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H115" s="5" t="n">
+        <v>-0.014215</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -8269,37 +8025,35 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Cash flows used in investing activities</t>
+          <t>Cash flows from (used in) financing activities</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures (note 6)</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>NetOtherInvestingChanges</t>
-        </is>
-      </c>
-      <c r="E116" s="5" t="n">
-        <v>-1.547</v>
-      </c>
-      <c r="F116" s="5" t="n">
-        <v>-26.581</v>
-      </c>
-      <c r="G116" s="5" t="n">
-        <v>-27.87</v>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Change in bank debt (note 12)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="n">
+        <v>0.075743</v>
+      </c>
+      <c r="I116" s="5" t="n">
+        <v>-0.015917</v>
       </c>
     </row>
     <row r="117">
@@ -8310,12 +8064,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Cash flows used in investing activities</t>
+          <t>Cash flows from (used in) financing activities</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Acquisition (note 4a)</t>
+          <t>Net cash flows from (used in) financing activities</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -8329,18 +8083,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G117" s="5" t="n">
-        <v>-33.173</v>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="n">
+        <v>0.07979700000000001</v>
+      </c>
+      <c r="I117" s="5" t="n">
+        <v>-0.016293</v>
       </c>
     </row>
     <row r="118">
@@ -8356,7 +8108,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Proceeds from dispositions (note 4b)</t>
+          <t>Development and production expenditures (note 4)</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -8370,18 +8122,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G118" s="5" t="n">
-        <v>7.99</v>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H118" s="5" t="n">
+        <v>-0.09068</v>
+      </c>
+      <c r="I118" s="5" t="n">
+        <v>-0.1226</v>
       </c>
     </row>
     <row r="119">
@@ -8397,32 +8147,30 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital (note 14)</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>ChangeInWorkingCapital</t>
-        </is>
-      </c>
-      <c r="E119" s="5" t="n">
-        <v>5.519</v>
-      </c>
-      <c r="F119" s="5" t="n">
-        <v>7.941</v>
-      </c>
-      <c r="G119" s="5" t="n">
-        <v>2.359</v>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Corporate expenditures (note 4)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H119" s="5" t="n">
+        <v>-0.003097</v>
+      </c>
+      <c r="I119" s="5" t="n">
+        <v>-0.000529</v>
       </c>
     </row>
     <row r="120">
@@ -8438,32 +8186,34 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Net cash flows used in investing activities</t>
+          <t>Exploration and evaluation expenditures (note 5)</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
-      <c r="E120" s="5" t="n">
-        <v>-67.161</v>
-      </c>
-      <c r="F120" s="5" t="n">
-        <v>-86.26600000000001</v>
-      </c>
-      <c r="G120" s="5" t="n">
-        <v>-94.354</v>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="n">
+        <v>-0.015129</v>
+      </c>
+      <c r="I120" s="5" t="n">
+        <v>-0.007373</v>
       </c>
     </row>
     <row r="121">
@@ -8479,27 +8229,27 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Change in cash and cash equivalents</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E121" s="5" t="n">
-        <v>15.287</v>
-      </c>
-      <c r="F121" s="5" t="n">
-        <v>-13.337</v>
-      </c>
-      <c r="G121" s="5" t="n">
-        <v>-1.95</v>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Acquisitions (note 4c)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="n">
+        <v>-0.062732</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -8520,34 +8270,32 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of year</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Proceeds from dispositions (note 4c)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F122" s="5" t="n">
-        <v>15.287</v>
-      </c>
-      <c r="G122" s="5" t="n">
-        <v>1.95</v>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I122" s="5" t="n">
+        <v>0.007791</v>
       </c>
     </row>
     <row r="123">
@@ -8563,34 +8311,34 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of year $</t>
+          <t>Change in non-cash working capital (note 16)</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E123" s="5" t="n">
-        <v>15.287</v>
-      </c>
-      <c r="F123" s="5" t="n">
-        <v>1.95</v>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H123" s="5" t="n">
+        <v>-0.001392</v>
+      </c>
+      <c r="I123" s="5" t="n">
+        <v>0.007653</v>
       </c>
     </row>
     <row r="124">
@@ -8601,35 +8349,33 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Accounting Standards Board (“IASB”).</t>
+          <t>Cash flows used in investing activities</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>These consolidated financial statements of the Company were approved and authorized for issue by the Board of Directors on March</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net cash flows used in investing activities</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="n">
+        <v>-67.161</v>
       </c>
       <c r="F124" s="5" t="n">
-        <v>2.024</v>
+        <v>-86.26600000000001</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-94.354</v>
+      </c>
+      <c r="H124" s="5" t="n">
+        <v>-0.17303</v>
+      </c>
+      <c r="I124" s="5" t="n">
+        <v>-0.115058</v>
       </c>
     </row>
     <row r="125">
@@ -8640,17 +8386,23 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Adjustments to add (deduct) non-cash items</t>
+          <t>Cash flows used in investing activities</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Gain related to deferred tax on acquisition (note 4)</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" s="5" t="n">
-        <v>-9.146000000000001</v>
+          <t>Change in cash</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -8662,15 +8414,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H125" s="5" t="n">
+        <v>0.002555</v>
+      </c>
+      <c r="I125" s="5" t="n">
+        <v>-0.002555</v>
       </c>
     </row>
     <row r="126">
@@ -8681,22 +8429,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Adjustments to add (deduct) non-cash items</t>
+          <t>Cash flows used in investing activities</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Deferred tax recovery (note 12)</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr"/>
+          <t>Cash, beginning of year</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F126" s="5" t="n">
-        <v>-14.797</v>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -8708,10 +8462,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I126" s="5" t="n">
+        <v>0.002555</v>
       </c>
     </row>
     <row r="127">
@@ -8722,30 +8474,36 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Adjustments to add (deduct) non-cash items</t>
+          <t>Cash flows used in investing activities</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Unrealized (gain) loss on risk management contracts</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" s="5" t="n">
-        <v>1.337</v>
-      </c>
-      <c r="F127" s="5" t="n">
-        <v>-2.025</v>
+          <t>Cash, end of year $</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H127" s="5" t="n">
+        <v>0.002555</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -8761,35 +8519,31 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Adjustments to add (deduct) non-cash items</t>
+          <t>Accounting Standards Board (“IASB”).</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Finance - accretion on decommissioning obligations (note 13)</t>
+          <t>These consolidated financial statements of the Company were approved and authorized for issue by the Board of Directors on March</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
-      <c r="E128" s="5" t="n">
-        <v>0.006</v>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F128" s="5" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.024</v>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="H128" s="5" t="n">
+        <v>0.002026</v>
+      </c>
+      <c r="I128" s="5" t="n">
+        <v>1e-05</v>
       </c>
     </row>
     <row r="129">
@@ -8800,35 +8554,35 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>i)   Reserves</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Common shares issued</t>
+          <t>Canadian Oil and Gas Evaluation "COGE" Handbook. The Company obtained an annual evaluation from  its independent third-party reserve evaluators to estimate proved and probable oil and gas reserves and the related cash flows on December</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
-      <c r="E129" s="5" t="n">
-        <v>83.47</v>
-      </c>
-      <c r="F129" s="5" t="n">
-        <v>38.744</v>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H129" s="5" t="n">
+        <v>0.002025</v>
+      </c>
+      <c r="I129" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="130">
@@ -8839,29 +8593,25 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>RUBELLITE ENERGY INC.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Share issue costs</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
-      <c r="E130" s="5" t="n">
-        <v>-2.137</v>
+          <t>Years Ended December 31, 2023 December</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F130" s="5" t="n">
-        <v>-1.685</v>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.022</v>
+      </c>
+      <c r="G130" s="5" t="n">
+        <v>0.031</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -8882,27 +8632,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Cash flows used in investing activities</t>
+          <t>Adjustments to add (deduct) non-cash items</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Cash from acquisitions (note 4)</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
+          <t>Depletion (note 5)</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Depletion</t>
+        </is>
+      </c>
       <c r="E131" s="5" t="n">
-        <v>-55.322</v>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.389</v>
+      </c>
+      <c r="F131" s="5" t="n">
+        <v>13.462</v>
+      </c>
+      <c r="G131" s="5" t="n">
+        <v>27.485</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -8923,25 +8673,27 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Cash flows used in investing activities</t>
+          <t>Adjustments to add (deduct) non-cash items</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>December</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
+          <t>Share-based payments (note 9)</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E132" s="5" t="n">
-        <v>2.021</v>
+        <v>0.307</v>
       </c>
       <c r="F132" s="5" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.724</v>
+      </c>
+      <c r="G132" s="5" t="n">
+        <v>3.041</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -8962,25 +8714,29 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>1.  REPORTING ENTITY</t>
+          <t>Adjustments to add (deduct) non-cash items</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>effective date of the Plan of Arrangement ("the Arrangement") involving Perpetual Energy Inc. ("Perpetual"), the shareholders of Perpetual and Rubellite, to December</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" s="5" t="n">
-        <v>2.021</v>
+          <t>Deferred tax expense (recovery) (note 12)</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F133" s="5" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-14.797</v>
+      </c>
+      <c r="G133" s="5" t="n">
+        <v>8.042</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -9001,25 +8757,25 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Material transactions</t>
+          <t>Adjustments to add (deduct) non-cash items</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Rubellite were delivered to Perpetual as part of the purchase consideration (note 4). The trading of Rubellite shares held by Rubellite shareholders commenced on September</t>
+          <t>Unrealized gain on risk management contracts (note 15)</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
-      <c r="E134" s="5" t="n">
-        <v>2.021</v>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F134" s="5" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.025</v>
+      </c>
+      <c r="G134" s="5" t="n">
+        <v>-8.651999999999999</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -9040,25 +8796,23 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Material transactions</t>
+          <t>Adjustments to add (deduct) non-cash items</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Operating results reflect the period from September 3, 2021, the effective date of the completion of the Arrangement, to December</t>
+          <t>Finance - accretion on decommissioning obligations (note 7)</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" s="5" t="n">
-        <v>2.021</v>
+        <v>0.006</v>
       </c>
       <c r="F135" s="5" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.067</v>
+      </c>
+      <c r="G135" s="5" t="n">
+        <v>0.128</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -9079,25 +8833,27 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>International Accounting Standards Board (“IASB”).</t>
+          <t>Adjustments to add (deduct) non-cash items</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>These consolidated financial statements of the Company were approved and authorized for issue by the Board of Directors on March</t>
+          <t>Gain on dispositions (note 4b)</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
-      <c r="E136" s="5" t="n">
-        <v>2.023</v>
-      </c>
-      <c r="F136" s="5" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="n">
+        <v>-1.29</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -9123,22 +8879,26 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Change in fair value of derivatives</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" s="5" t="n">
-        <v>1.337</v>
+          <t>Exploration and evaluation expense (note 6)</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G137" s="5" t="n">
+        <v>6.842</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -9159,31 +8919,27 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Cash flows used in investing activities</t>
+          <t>Adjustments to add (deduct) non-cash items</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Capital expenditures (note 5, 6)</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>CapitalExpenditure</t>
-        </is>
-      </c>
-      <c r="E138" s="5" t="n">
-        <v>-17.358</v>
+          <t>Decommissioning obligations settled (note 7)</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G138" s="5" t="n">
+        <v>-0.003</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -9204,27 +8960,27 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Cash flows used in investing activities</t>
+          <t>Adjustments to add (deduct) non-cash items</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Acquisitions, net of cash received (note 4)</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr"/>
+          <t>Change in non-cash working capital (note 14)</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E139" s="5" t="n">
-        <v>-55.322</v>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.48</v>
+      </c>
+      <c r="F139" s="5" t="n">
+        <v>0.834</v>
+      </c>
+      <c r="G139" s="5" t="n">
+        <v>1.237</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -9245,33 +9001,27 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Cash flows used in investing activities</t>
+          <t>Adjustments to add (deduct) non-cash items</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of period</t>
+          <t>Net cash flows from operating activities</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="n">
+        <v>1.115</v>
+      </c>
+      <c r="F140" s="5" t="n">
+        <v>23.87</v>
+      </c>
+      <c r="G140" s="5" t="n">
+        <v>55.391</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -9292,31 +9042,25 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Cash flows used in investing activities</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of period $</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E141" s="5" t="n">
-        <v>15.287</v>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Common shares issued (note 8)</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F141" s="5" t="n">
+        <v>38.744</v>
+      </c>
+      <c r="G141" s="5" t="n">
+        <v>19.95</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -9337,27 +9081,29 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Material transactions</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Clearwater assets were acquired for aggregate consideration of $65.5 million. The consideration consisted of promissory notes totaling</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" s="5" t="n">
-        <v>0.0594</v>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share issue costs (note 8)</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F142" s="5" t="n">
+        <v>-1.685</v>
+      </c>
+      <c r="G142" s="5" t="n">
+        <v>-0.254</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -9378,27 +9124,25 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Material transactions</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>million, which were paid in cash on October 5, 2021, the issuance of 680,485 Rubellite common shares valued at $1.3 million, the return of</t>
+          <t>Change in revolving bank debt (note 11)</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
-      <c r="E143" s="5" t="n">
-        <v>0.008200000000000001</v>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F143" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G143" s="5" t="n">
+        <v>17.317</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -9419,27 +9163,27 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>International Accounting Standards Board (“IASB”).</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>These consolidated financial statements of the Company were approved and authorized for issue by the Board of Directors on March 9,</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr"/>
+          <t>Net cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E144" s="5" t="n">
-        <v>2.022</v>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>81.333</v>
+      </c>
+      <c r="F144" s="5" t="n">
+        <v>49.059</v>
+      </c>
+      <c r="G144" s="5" t="n">
+        <v>37.013</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -9455,30 +9199,28 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>RUBELLITE ENERGY INC.</t>
+          <t>Cash flows used in investing activities</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Years Ended December 31, 2023 December</t>
+          <t>Property, plant and equipment expenditures (note 5)</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E145" s="5" t="n">
+        <v>-15.811</v>
       </c>
       <c r="F145" s="5" t="n">
-        <v>2.022</v>
+        <v>-67.626</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>0.031</v>
+        <v>-43.66</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -9494,28 +9236,32 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Cash flows used in investing activities</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Oil (note 10) $</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr"/>
+          <t>Exploration and evaluation expenditures (note 6)</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E146" s="5" t="n">
-        <v>4.923</v>
+        <v>-1.547</v>
       </c>
       <c r="F146" s="5" t="n">
-        <v>54.491</v>
+        <v>-26.581</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>88.968</v>
+        <v>-27.87</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -9531,28 +9277,32 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Cash flows used in investing activities</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Royalties</t>
+          <t>Acquisition (note 4a)</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
-      <c r="E147" s="5" t="n">
-        <v>-0.491</v>
-      </c>
-      <c r="F147" s="5" t="n">
-        <v>-5.713</v>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G147" s="5" t="n">
-        <v>-8.513</v>
+        <v>-33.173</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -9568,32 +9318,32 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Cash flows used in investing activities</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Revenue total</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E148" s="5" t="n">
-        <v>4.432</v>
-      </c>
-      <c r="F148" s="5" t="n">
-        <v>48.778</v>
+          <t>Proceeds from dispositions (note 4b)</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G148" s="5" t="n">
-        <v>80.455</v>
+        <v>7.99</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -9609,30 +9359,32 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Cash flows used in investing activities</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Realized loss on risk management contracts (note 15)</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Change in non-cash working capital (note 14)</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="n">
+        <v>5.519</v>
       </c>
       <c r="F149" s="5" t="n">
-        <v>-13.142</v>
+        <v>7.941</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>-0.318</v>
+        <v>2.359</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -9648,30 +9400,32 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Cash flows used in investing activities</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Unrealized gain on risk management contracts (note 15)</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Change in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E150" s="5" t="n">
+        <v>15.287</v>
       </c>
       <c r="F150" s="5" t="n">
-        <v>2.025</v>
+        <v>-13.337</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>8.651999999999999</v>
+        <v>-1.95</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -9687,28 +9441,34 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows used in investing activities</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Production and operating</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" s="5" t="n">
-        <v>0.802</v>
+          <t>Cash and cash equivalents, beginning of year</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F151" s="5" t="n">
-        <v>4.399</v>
+        <v>15.287</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>7.371</v>
+        <v>1.95</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -9724,28 +9484,34 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows used in investing activities</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Transportation</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
+          <t>Cash and cash equivalents, end of year $</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E152" s="5" t="n">
-        <v>0.41</v>
+        <v>15.287</v>
       </c>
       <c r="F152" s="5" t="n">
-        <v>4.448</v>
-      </c>
-      <c r="G152" s="5" t="n">
-        <v>9.045</v>
+        <v>1.95</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -9761,34 +9527,32 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments to add (deduct) non-cash items</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>General and administrative</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F153" s="5" t="n">
-        <v>3.316</v>
-      </c>
-      <c r="G153" s="5" t="n">
-        <v>7.318</v>
+          <t>Gain related to deferred tax on acquisition (note 4)</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" s="5" t="n">
+        <v>-9.146000000000001</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -9804,28 +9568,36 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments to add (deduct) non-cash items</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Share based payments (note 9)</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr"/>
-      <c r="E154" s="5" t="n">
-        <v>0.307</v>
+          <t>Deferred tax recovery (note 12)</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F154" s="5" t="n">
-        <v>1.724</v>
-      </c>
-      <c r="G154" s="5" t="n">
-        <v>3.041</v>
+        <v>-14.797</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -9841,30 +9613,30 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments to add (deduct) non-cash items</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Exploration and evaluation (note 6)</t>
+          <t>Unrealized (gain) loss on risk management contracts</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E155" s="5" t="n">
+        <v>1.337</v>
       </c>
       <c r="F155" s="5" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="G155" s="5" t="n">
-        <v>7.018</v>
+        <v>-2.025</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -9880,32 +9652,30 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments to add (deduct) non-cash items</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Gain on dispositions (note 4b)</t>
+          <t>Finance - accretion on decommissioning obligations (note 13)</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G156" s="5" t="n">
-        <v>-1.29</v>
+      <c r="E156" s="5" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="F156" s="5" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -9921,32 +9691,30 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Depletion (note 5)</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>Depletion</t>
-        </is>
-      </c>
+          <t>Common shares issued</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" s="5" t="n">
-        <v>1.389</v>
+        <v>83.47</v>
       </c>
       <c r="F157" s="5" t="n">
-        <v>13.462</v>
-      </c>
-      <c r="G157" s="5" t="n">
-        <v>27.485</v>
+        <v>38.744</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -9962,32 +9730,34 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Transaction costs (note 4a)</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G158" s="5" t="n">
-        <v>0.147</v>
+          <t>Share issue costs</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
+      <c r="E158" s="5" t="n">
+        <v>-2.137</v>
+      </c>
+      <c r="F158" s="5" t="n">
+        <v>-1.685</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -10003,32 +9773,32 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows used in investing activities</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Expenses total</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Cash from acquisitions (note 4)</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" s="5" t="n">
-        <v>7.688</v>
-      </c>
-      <c r="F159" s="5" t="n">
-        <v>10.218</v>
-      </c>
-      <c r="G159" s="5" t="n">
-        <v>28.654</v>
+        <v>-55.322</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -10044,30 +9814,30 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows used in investing activities</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Finance expense (note 13)</t>
+          <t>December</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E160" s="5" t="n">
+        <v>2.021</v>
       </c>
       <c r="F160" s="5" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="G160" s="5" t="n">
-        <v>-2.051</v>
+        <v>0.031</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -10083,32 +9853,30 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>1.  REPORTING ENTITY</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Income before income tax</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>effective date of the Plan of Arrangement ("the Arrangement") involving Perpetual Energy Inc. ("Perpetual"), the shareholders of Perpetual and Rubellite, to December</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
       <c r="E161" s="5" t="n">
-        <v>7.702</v>
+        <v>2.021</v>
       </c>
       <c r="F161" s="5" t="n">
-        <v>9.808</v>
-      </c>
-      <c r="G161" s="5" t="n">
-        <v>26.603</v>
+        <v>0.031</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -10124,30 +9892,30 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Taxes</t>
+          <t>Material transactions</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Deferred tax (expense) recovery (note 12)</t>
+          <t>Rubellite were delivered to Perpetual as part of the purchase consideration (note 4). The trading of Rubellite shares held by Rubellite shareholders commenced on September</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E162" s="5" t="n">
+        <v>2.021</v>
       </c>
       <c r="F162" s="5" t="n">
-        <v>14.797</v>
-      </c>
-      <c r="G162" s="5" t="n">
-        <v>-8.042</v>
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -10163,34 +9931,30 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Taxes</t>
+          <t>Material transactions</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Net income and comprehensive income $</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Operating results reflect the period from September 3, 2021, the effective date of the completion of the Arrangement, to December</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" s="5" t="n">
+        <v>2.021</v>
       </c>
       <c r="F163" s="5" t="n">
-        <v>24.605</v>
-      </c>
-      <c r="G163" s="5" t="n">
-        <v>18.561</v>
+        <v>0.031</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -10206,32 +9970,30 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Net income per share</t>
+          <t>International Accounting Standards Board (“IASB”).</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Basic $</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>These consolidated financial statements of the Company were approved and authorized for issue by the Board of Directors on March</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
       <c r="E164" s="5" t="n">
-        <v>3.4e-07</v>
+        <v>2.023</v>
       </c>
       <c r="F164" s="5" t="n">
-        <v>4.699999999999999e-07</v>
-      </c>
-      <c r="G164" s="5" t="n">
-        <v>3.1e-07</v>
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -10247,32 +10009,32 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Net income per share</t>
+          <t>Adjustments to add (deduct) non-cash items</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Diluted $</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>DilutedEPS</t>
-        </is>
-      </c>
+          <t>Change in fair value of derivatives</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
       <c r="E165" s="5" t="n">
-        <v>3.3e-07</v>
-      </c>
-      <c r="F165" s="5" t="n">
-        <v>4.699999999999999e-07</v>
-      </c>
-      <c r="G165" s="5" t="n">
-        <v>3e-07</v>
+        <v>1.337</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -10288,25 +10050,31 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Cash flows used in investing activities</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Realized gain (loss) on risk management contracts (note 15)</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr"/>
+          <t>Capital expenditures (note 5, 6)</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>CapitalExpenditure</t>
+        </is>
+      </c>
       <c r="E166" s="5" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="F166" s="5" t="n">
-        <v>-13.142</v>
+        <v>-17.358</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -10327,25 +10095,27 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Cash flows used in investing activities</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Unrealized gain (loss) on risk management contracts (note 15)</t>
+          <t>Acquisitions, net of cash received (note 4)</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" s="5" t="n">
-        <v>-1.337</v>
-      </c>
-      <c r="F167" s="5" t="n">
-        <v>2.025</v>
+        <v>-55.322</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -10366,29 +10136,33 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows used in investing activities</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>General and administrative (note 17)</t>
+          <t>Cash and cash equivalents, beginning of period</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E168" s="5" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="F168" s="5" t="n">
-        <v>3.316</v>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -10409,22 +10183,26 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows used in investing activities</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Transaction costs (note 4)</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr"/>
+          <t>Cash and cash equivalents, end of period $</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E169" s="5" t="n">
-        <v>1.071</v>
+        <v>15.287</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -10450,22 +10228,22 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Material transactions</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Gain related to deferred tax on acquisition (note 4)</t>
+          <t>Clearwater assets were acquired for aggregate consideration of $65.5 million. The consideration consisted of promissory notes totaling</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
       <c r="E170" s="5" t="n">
-        <v>-9.146000000000001</v>
+        <v>0.0594</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -10491,25 +10269,27 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Material transactions</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Finance income (expense) (note 13)</t>
+          <t>million, which were paid in cash on October 5, 2021, the issuance of 680,485 Rubellite common shares valued at $1.3 million, the return of</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
       <c r="E171" s="5" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="F171" s="5" t="n">
-        <v>-0.41</v>
+        <v>0.008200000000000001</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
@@ -10530,27 +10310,27 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Taxes</t>
+          <t>International Accounting Standards Board (“IASB”).</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Deferred tax recovery (note 12)</t>
+          <t>These consolidated financial statements of the Company were approved and authorized for issue by the Board of Directors on March 9,</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F172" s="5" t="n">
-        <v>14.797</v>
+      <c r="E172" s="5" t="n">
+        <v>2.022</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -10576,39 +10356,35 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Taxes</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Net income $</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E173" s="5" t="n">
-        <v>7.702</v>
-      </c>
-      <c r="F173" s="5" t="n">
-        <v>24.605</v>
+          <t>Oil and natural gas (note 11) $</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H173" s="5" t="n">
+        <v>0.168384</v>
+      </c>
+      <c r="I173" s="5" t="n">
+        <v>0.2417</v>
       </c>
     </row>
     <row r="174">
@@ -10619,35 +10395,29 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Net income per share</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>December</t>
+          <t>Royalties</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
       <c r="E174" s="5" t="n">
-        <v>2.021</v>
+        <v>-0.491</v>
       </c>
       <c r="F174" s="5" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-5.713</v>
+      </c>
+      <c r="G174" s="5" t="n">
+        <v>-8.513</v>
+      </c>
+      <c r="H174" s="5" t="n">
+        <v>-0.020272</v>
+      </c>
+      <c r="I174" s="5" t="n">
+        <v>-0.032454</v>
       </c>
     </row>
     <row r="175">
@@ -10663,32 +10433,28 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Oil and natural gas (note 10) $</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
+          <t>Revenue total</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E175" s="5" t="n">
-        <v>4.923</v>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.432</v>
+      </c>
+      <c r="F175" s="5" t="n">
+        <v>48.778</v>
+      </c>
+      <c r="G175" s="5" t="n">
+        <v>80.455</v>
+      </c>
+      <c r="H175" s="5" t="n">
+        <v>0.148112</v>
+      </c>
+      <c r="I175" s="5" t="n">
+        <v>0.209246</v>
       </c>
     </row>
     <row r="176">
@@ -10704,12 +10470,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Realized gain on derivatives (note 15)</t>
+          <t>Realized gain on risk management contracts (note 17)</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
-      <c r="E176" s="5" t="n">
-        <v>0.101</v>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -10721,15 +10489,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H176" s="5" t="n">
+        <v>0.002582</v>
+      </c>
+      <c r="I176" s="5" t="n">
+        <v>0.011371</v>
       </c>
     </row>
     <row r="177">
@@ -10745,12 +10509,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Change in fair value of derivatives (note 15)</t>
+          <t>Unrealized loss on risk management contracts (note 17)</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
-      <c r="E177" s="5" t="n">
-        <v>-1.337</v>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -10762,15 +10528,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H177" s="5" t="n">
+        <v>-0.012252</v>
+      </c>
+      <c r="I177" s="5" t="n">
+        <v>-0.001721</v>
       </c>
     </row>
     <row r="178">
@@ -10781,21 +10543,23 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>General and administrative (note 4)</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E178" s="5" t="n">
-        <v>0.675</v>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -10807,15 +10571,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H178" s="5" t="n">
+        <v>0.000178</v>
+      </c>
+      <c r="I178" s="5" t="n">
+        <v>0.000827</v>
       </c>
     </row>
     <row r="179">
@@ -10831,36 +10591,24 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Finance income (note 13)</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Production and operating</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
       <c r="E179" s="5" t="n">
-        <v>-0.014</v>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.802</v>
+      </c>
+      <c r="F179" s="5" t="n">
+        <v>4.399</v>
+      </c>
+      <c r="G179" s="5" t="n">
+        <v>7.371</v>
+      </c>
+      <c r="H179" s="5" t="n">
+        <v>0.016692</v>
+      </c>
+      <c r="I179" s="5" t="n">
+        <v>0.029946</v>
       </c>
     </row>
     <row r="180">
@@ -10871,43 +10619,29 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Taxes</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Deferred income tax expense (note 12)</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Transportation</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" s="5" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F180" s="5" t="n">
+        <v>4.448</v>
+      </c>
+      <c r="G180" s="5" t="n">
+        <v>9.045</v>
+      </c>
+      <c r="H180" s="5" t="n">
+        <v>0.016328</v>
+      </c>
+      <c r="I180" s="5" t="n">
+        <v>0.023623</v>
       </c>
     </row>
     <row r="181">
@@ -10918,41 +10652,35 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Taxes</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Net income and comprehensive income</t>
+          <t>General and administrative</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E181" s="5" t="n">
-        <v>7.702</v>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F181" s="5" t="n">
+        <v>3.316</v>
+      </c>
+      <c r="G181" s="5" t="n">
+        <v>7.318</v>
+      </c>
+      <c r="H181" s="5" t="n">
+        <v>0.010616</v>
+      </c>
+      <c r="I181" s="5" t="n">
+        <v>0.015875</v>
       </c>
     </row>
     <row r="182">
@@ -10963,17 +10691,19 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Taxes</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Net income per share (note</t>
+          <t>Share based payments (note 10)</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
-      <c r="E182" s="5" t="n">
-        <v>8e-06</v>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -10985,15 +10715,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H182" s="5" t="n">
+        <v>0.003571</v>
+      </c>
+      <c r="I182" s="5" t="n">
+        <v>0.005368</v>
       </c>
     </row>
     <row r="183">
@@ -11004,17 +10730,19 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Taxes</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Basic $</t>
+          <t>Exploration and evaluation (note 5)</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
-      <c r="E183" s="5" t="n">
-        <v>0.00034</v>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -11026,15 +10754,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H183" s="5" t="n">
+        <v>0.000541</v>
+      </c>
+      <c r="I183" s="5" t="n">
+        <v>0.005543</v>
       </c>
     </row>
     <row r="184">
@@ -11045,34 +10769,1603 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Gain on disposition (note 4c)</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H184" s="5" t="n">
+        <v>-0.031617</v>
+      </c>
+      <c r="I184" s="5" t="n">
+        <v>-0.007791</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Depletion and depreciation (note 4, 6)</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H185" s="5" t="n">
+        <v>0.049847</v>
+      </c>
+      <c r="I185" s="5" t="n">
+        <v>0.09424299999999999</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Transaction costs</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H186" s="5" t="n">
+        <v>0.006233</v>
+      </c>
+      <c r="I186" s="5" t="n">
+        <v>0.000132</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E187" s="5" t="n">
+        <v>7.688</v>
+      </c>
+      <c r="F187" s="5" t="n">
+        <v>10.218</v>
+      </c>
+      <c r="G187" s="5" t="n">
+        <v>28.654</v>
+      </c>
+      <c r="H187" s="5" t="n">
+        <v>0.066409</v>
+      </c>
+      <c r="I187" s="5" t="n">
+        <v>0.052784</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Finance expense (note 15)</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H188" s="5" t="n">
+        <v>-0.007376</v>
+      </c>
+      <c r="I188" s="5" t="n">
+        <v>-0.011343</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Income before income tax</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E189" s="5" t="n">
+        <v>7.702</v>
+      </c>
+      <c r="F189" s="5" t="n">
+        <v>9.808</v>
+      </c>
+      <c r="G189" s="5" t="n">
+        <v>26.603</v>
+      </c>
+      <c r="H189" s="5" t="n">
+        <v>0.059033</v>
+      </c>
+      <c r="I189" s="5" t="n">
+        <v>0.041441</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
           <t>Taxes</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr">
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Deferred expense (note 14)</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H190" s="5" t="n">
+        <v>-0.00906</v>
+      </c>
+      <c r="I190" s="5" t="n">
+        <v>-0.008884</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Taxes</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Net income and comprehensive income $</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F191" s="5" t="n">
+        <v>24.605</v>
+      </c>
+      <c r="G191" s="5" t="n">
+        <v>18.561</v>
+      </c>
+      <c r="H191" s="5" t="n">
+        <v>0.049973</v>
+      </c>
+      <c r="I191" s="5" t="n">
+        <v>0.032557</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Net income per share</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Basic $</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E192" s="5" t="n">
+        <v>3.4e-07</v>
+      </c>
+      <c r="F192" s="5" t="n">
+        <v>4.699999999999999e-07</v>
+      </c>
+      <c r="G192" s="5" t="n">
+        <v>3.1e-07</v>
+      </c>
+      <c r="H192" s="5" t="n">
+        <v>7.3e-07</v>
+      </c>
+      <c r="I192" s="5" t="n">
+        <v>3.5e-07</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Net income per share</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
         <is>
           <t>Diluted $</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
-      <c r="E184" s="5" t="n">
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>DilutedEPS</t>
+        </is>
+      </c>
+      <c r="E193" s="5" t="n">
+        <v>3.3e-07</v>
+      </c>
+      <c r="F193" s="5" t="n">
+        <v>4.699999999999999e-07</v>
+      </c>
+      <c r="G193" s="5" t="n">
+        <v>3e-07</v>
+      </c>
+      <c r="H193" s="5" t="n">
+        <v>7.2e-07</v>
+      </c>
+      <c r="I193" s="5" t="n">
+        <v>3.4e-07</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>RUBELLITE ENERGY INC.</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Years Ended December 31, 2023 December</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F194" s="5" t="n">
+        <v>2.022</v>
+      </c>
+      <c r="G194" s="5" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Oil (note 10) $</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" s="5" t="n">
+        <v>4.923</v>
+      </c>
+      <c r="F195" s="5" t="n">
+        <v>54.491</v>
+      </c>
+      <c r="G195" s="5" t="n">
+        <v>88.968</v>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Realized loss on risk management contracts (note 15)</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F196" s="5" t="n">
+        <v>-13.142</v>
+      </c>
+      <c r="G196" s="5" t="n">
+        <v>-0.318</v>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Unrealized gain on risk management contracts (note 15)</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F197" s="5" t="n">
+        <v>2.025</v>
+      </c>
+      <c r="G197" s="5" t="n">
+        <v>8.651999999999999</v>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Share based payments (note 9)</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" s="5" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="F198" s="5" t="n">
+        <v>1.724</v>
+      </c>
+      <c r="G198" s="5" t="n">
+        <v>3.041</v>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Exploration and evaluation (note 6)</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F199" s="5" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="G199" s="5" t="n">
+        <v>7.018</v>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Gain on dispositions (note 4b)</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G200" s="5" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Depletion (note 5)</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Depletion</t>
+        </is>
+      </c>
+      <c r="E201" s="5" t="n">
+        <v>1.389</v>
+      </c>
+      <c r="F201" s="5" t="n">
+        <v>13.462</v>
+      </c>
+      <c r="G201" s="5" t="n">
+        <v>27.485</v>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Transaction costs (note 4a)</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G202" s="5" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Finance expense (note 13)</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F203" s="5" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="G203" s="5" t="n">
+        <v>-2.051</v>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Taxes</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Deferred tax (expense) recovery (note 12)</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F204" s="5" t="n">
+        <v>14.797</v>
+      </c>
+      <c r="G204" s="5" t="n">
+        <v>-8.042</v>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Realized gain (loss) on risk management contracts (note 15)</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" s="5" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="F205" s="5" t="n">
+        <v>-13.142</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Unrealized gain (loss) on risk management contracts (note 15)</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" s="5" t="n">
+        <v>-1.337</v>
+      </c>
+      <c r="F206" s="5" t="n">
+        <v>2.025</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>General and administrative (note 17)</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E207" s="5" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="F207" s="5" t="n">
+        <v>3.316</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Transaction costs (note 4)</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" s="5" t="n">
+        <v>1.071</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Gain related to deferred tax on acquisition (note 4)</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" s="5" t="n">
+        <v>-9.146000000000001</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Finance income (expense) (note 13)</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" s="5" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="F210" s="5" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Taxes</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Deferred tax recovery (note 12)</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F211" s="5" t="n">
+        <v>14.797</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Taxes</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Net income $</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E212" s="5" t="n">
+        <v>7.702</v>
+      </c>
+      <c r="F212" s="5" t="n">
+        <v>24.605</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Net income per share</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>December</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" s="5" t="n">
+        <v>2.021</v>
+      </c>
+      <c r="F213" s="5" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Oil and natural gas (note 10) $</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" s="5" t="n">
+        <v>4.923</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Realized gain on derivatives (note 15)</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" s="5" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Change in fair value of derivatives (note 15)</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" s="5" t="n">
+        <v>-1.337</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>General and administrative (note 4)</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E217" s="5" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Finance income (note 13)</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E218" s="5" t="n">
+        <v>-0.014</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Taxes</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Deferred income tax expense (note 12)</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Taxes</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Net income and comprehensive income</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E220" s="5" t="n">
+        <v>7.702</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Taxes</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Net income per share (note</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" s="5" t="n">
+        <v>8e-06</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Taxes</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Basic $</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" s="5" t="n">
+        <v>0.00034</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Taxes</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Diluted $</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" s="5" t="n">
         <v>0.00033</v>
       </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
         <is>
           <t>-</t>
         </is>
